--- a/Result/profitability/2380.xlsx
+++ b/Result/profitability/2380.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2575</v>
+        <v>-0.10875</v>
       </c>
       <c r="N2" t="n">
-        <v>23.45125</v>
+        <v>27.02875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.26</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.08</v>
+        <v>-0.008749999999999994</v>
       </c>
       <c r="N3" t="n">
-        <v>26.995</v>
+        <v>28.715</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04125</v>
+        <v>0.0425</v>
       </c>
       <c r="N4" t="n">
-        <v>29.25125</v>
+        <v>27.29125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0475</v>
+        <v>-0.03749999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>27.4725</v>
+        <v>25.3025</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.03249999999999999</v>
+        <v>0.002500000000000009</v>
       </c>
       <c r="N6" t="n">
-        <v>26.12625</v>
+        <v>25.68</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,16 +1264,16 @@
         <v>-0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.02749999999999999</v>
+        <v>0.10125</v>
       </c>
       <c r="N7" t="n">
-        <v>25.95125</v>
+        <v>25.525</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1175</v>
+        <v>0.07125000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>26.90625</v>
+        <v>24.705</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.19</v>
       </c>
       <c r="M12" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="N12" t="n">
         <v>29.27625</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>816</v>
+      </c>
+      <c r="D75" t="n">
+        <v>645</v>
+      </c>
+      <c r="E75" t="n">
+        <v>171</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-43</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.22375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.90625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.925</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-17.61</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4560994560994561</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.6799999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9577464788732395</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-17.36</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4525547445255474</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
